--- a/audit_report_ALL_TEAM_21_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -841,20 +841,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Pramod Sapkota</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9841509605</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9841509605</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +863,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9841509605</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9841509605</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +881,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.672256</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.672256</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -948,25 +938,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.373051</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.373051</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv related issue   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1062,10 +1048,8 @@
           <t>Saman Lamichhane</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9813824865</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9813824865</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1080,10 +1064,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9813824865</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9813824865</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1100,10 +1082,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.676466</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.676466</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1155,25 +1135,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L3-4</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.363121</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.36312100000001</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1222,7 +1198,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1554,7 +1530,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv related issue   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_21_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1173,6 +1173,424 @@
         </is>
       </c>
       <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 1:05 PM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375301</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Kishor Shrestha</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Kishor Shrestha</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9851060333</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 11:41:51 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9818332206</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 11:41:51 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 01:05:41 PM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.69469</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Next to Agni Motoinc Pvt. Ltd, Teku, kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>kishor9851060333@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>11:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>CDB043</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.30412</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 23m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 23m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 1:04 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375528</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Bhola Ram Khadka</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Bhola Ram Khadka</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9801055714</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 07:43:24 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9851037495</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 07:43:24 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 01:04:18 PM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.758847</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Unnamed Road, Q85W+7VJ, ??????????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>03:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.346056</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>17h 20m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>17h 20m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1189,7 +1607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1198,7 +1616,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1226,7 +1644,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1654,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1247,7 +1665,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1677,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>15m</t>
+          <t>14h 20m</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1689,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 50m</t>
+          <t>1d 4h 51m</t>
         </is>
       </c>
     </row>
@@ -1312,14 +1730,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1388,14 +1806,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1561,6 +1979,140 @@
       <c r="M20" s="3" t="inlineStr">
         <is>
           <t>1d 19h 50m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1375301</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Kishor Shrestha</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 11:41:51 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 11:41:51 AM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 01:05:41 PM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 23m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375528</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Bhola Ram Khadka</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 07:43:24 PM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 07:43:24 PM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 01:04:18 PM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>17h 20m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>17h 20m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_21_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_21_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1245,10 +1245,8 @@
           <t>Kishor Shrestha</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9851060333</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9851060333</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1263,10 +1261,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9818332206</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9818332206</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1283,10 +1279,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.69469</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.69469</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1342,25 +1336,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB043</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.30412</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.30412</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1456,10 +1446,8 @@
           <t>Bhola Ram Khadka</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9801055714</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9801055714</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1474,10 +1462,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9851037495</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9851037495</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1494,10 +1480,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.758847</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.758847</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1549,25 +1533,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L36-3</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.346056</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.346056</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1616,7 +1596,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2015,7 +1995,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -2082,7 +2062,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
